--- a/Output Files GPT-OSS 20B/Direct_LLM_Scoring_results_stats.xlsx
+++ b/Output Files GPT-OSS 20B/Direct_LLM_Scoring_results_stats.xlsx
@@ -665,13 +665,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="F4" t="n">
         <v>0.8</v>
@@ -745,7 +745,7 @@
         <v>0.8</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>0.5</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F6" t="n">
         <v>0.8</v>
@@ -878,16 +878,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="D7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E7" t="n">
         <v>0.5</v>
       </c>
-      <c r="E7" t="n">
-        <v>0.9</v>
-      </c>
       <c r="F7" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -949,16 +949,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D8" t="n">
         <v>0.5</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1023,13 +1023,13 @@
         <v>0.6</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E9" t="n">
         <v>0.8</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1097,10 +1097,10 @@
         <v>0.5</v>
       </c>
       <c r="E10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F10" t="n">
         <v>0.6</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.8</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1162,13 +1162,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="F11" t="n">
         <v>0.8</v>
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E12" t="n">
         <v>0.8</v>
@@ -1304,16 +1304,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F13" t="n">
         <v>0.9</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.8</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1378,13 +1378,13 @@
         <v>0.6</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E14" t="n">
         <v>0.8</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>0.6</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E15" t="n">
         <v>0.7</v>
@@ -1517,13 +1517,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D16" t="n">
         <v>0.5</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="F16" t="n">
         <v>0.8</v>
@@ -1588,16 +1588,16 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E17" t="n">
         <v>0.5</v>
       </c>
-      <c r="D17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.6</v>
-      </c>
       <c r="F17" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1659,16 +1659,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="E18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F18" t="n">
         <v>0.5</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.8</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1730,16 +1730,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -2014,16 +2014,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2091,10 +2091,10 @@
         <v>0.5</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="C25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E25" t="n">
         <v>0.6</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.7</v>
       </c>
       <c r="F25" t="n">
         <v>0.8</v>
@@ -2227,16 +2227,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="D26" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D27" t="n">
         <v>0.5</v>
@@ -2307,7 +2307,7 @@
         <v>0.8</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2372,13 +2372,13 @@
         <v>0.6</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E28" t="n">
         <v>0.8</v>
       </c>
       <c r="F28" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2440,16 +2440,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2511,16 +2511,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E30" t="n">
         <v>0.8</v>
       </c>
       <c r="F30" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="D31" t="n">
         <v>0.5</v>
@@ -2659,10 +2659,10 @@
         <v>0.6</v>
       </c>
       <c r="E32" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F32" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2727,10 +2727,10 @@
         <v>0.6</v>
       </c>
       <c r="D33" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E33" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="F33" t="n">
         <v>0.8</v>
@@ -2795,16 +2795,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="D34" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="E34" t="n">
         <v>0.6</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2866,13 +2866,13 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="D35" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="E35" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="F35" t="n">
         <v>0.8</v>
@@ -2937,13 +2937,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="D36" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E36" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F36" t="n">
         <v>0.8</v>
@@ -3011,13 +3011,13 @@
         <v>0.4</v>
       </c>
       <c r="D37" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E37" t="n">
         <v>0.5</v>
       </c>
-      <c r="E37" t="n">
-        <v>0.8</v>
-      </c>
       <c r="F37" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -3082,10 +3082,10 @@
         <v>0.4</v>
       </c>
       <c r="D38" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E38" t="n">
         <v>0.5</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.6</v>
       </c>
       <c r="F38" t="n">
         <v>0.7</v>
@@ -3150,16 +3150,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="D39" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F39" t="n">
         <v>0.5</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.7</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -3224,10 +3224,10 @@
         <v>0.4</v>
       </c>
       <c r="D40" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E40" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="F40" t="n">
         <v>0.5</v>
@@ -3298,7 +3298,7 @@
         <v>0.6</v>
       </c>
       <c r="E41" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F41" t="n">
         <v>0.8</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D42" t="n">
         <v>0.5</v>
@@ -3437,13 +3437,13 @@
         <v>0.6</v>
       </c>
       <c r="D43" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E43" t="n">
-        <v>0.8</v>
+        <v>0.55</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -3511,10 +3511,10 @@
         <v>0.5</v>
       </c>
       <c r="E44" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -3576,16 +3576,16 @@
         </is>
       </c>
       <c r="C45" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F45" t="n">
         <v>0.5</v>
-      </c>
-      <c r="D45" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E45" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0.8</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -3647,13 +3647,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="D46" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E46" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F46" t="n">
         <v>0.8</v>
@@ -3718,10 +3718,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="D47" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="E47" t="n">
         <v>0.5</v>
@@ -3798,7 +3798,7 @@
         <v>0.5</v>
       </c>
       <c r="F48" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -3866,10 +3866,10 @@
         <v>0.2</v>
       </c>
       <c r="E49" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="F49" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -3931,13 +3931,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="D50" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E50" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F50" t="n">
         <v>0.9</v>
@@ -4008,10 +4008,10 @@
         <v>0.5</v>
       </c>
       <c r="E51" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F51" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>0.6</v>
       </c>
       <c r="E52" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="F52" t="n">
         <v>0.8</v>
@@ -4144,16 +4144,16 @@
         </is>
       </c>
       <c r="C53" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F53" t="n">
         <v>0.5</v>
-      </c>
-      <c r="D53" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E53" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0.8</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -4215,16 +4215,16 @@
         </is>
       </c>
       <c r="C54" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D54" t="n">
         <v>0.5</v>
-      </c>
-      <c r="D54" t="n">
-        <v>0.3</v>
       </c>
       <c r="E54" t="n">
         <v>0.6</v>
       </c>
       <c r="F54" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -4286,16 +4286,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="D55" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="E55" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="F55" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -4357,16 +4357,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D56" t="n">
         <v>0.5</v>
       </c>
       <c r="E56" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="F56" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -4428,13 +4428,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D57" t="n">
         <v>0.5</v>
       </c>
       <c r="E57" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F57" t="n">
         <v>0.8</v>
@@ -4505,10 +4505,10 @@
         <v>0.6</v>
       </c>
       <c r="E58" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="F58" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -4573,13 +4573,13 @@
         <v>0.4</v>
       </c>
       <c r="D59" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E59" t="n">
         <v>0.5</v>
       </c>
-      <c r="E59" t="n">
-        <v>0.6</v>
-      </c>
       <c r="F59" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D60" t="n">
         <v>0.5</v>
@@ -4712,16 +4712,16 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="D61" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="E61" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F61" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -4783,16 +4783,16 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="D62" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="E62" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="F62" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -4854,16 +4854,16 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="D63" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E63" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F63" t="n">
         <v>0.9</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0.8</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -4931,10 +4931,10 @@
         <v>0.2</v>
       </c>
       <c r="E64" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F64" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -4996,16 +4996,16 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="D65" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="E65" t="n">
-        <v>0.8</v>
+        <v>0.55</v>
       </c>
       <c r="F65" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -5067,16 +5067,16 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D66" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E66" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="F66" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -5209,16 +5209,16 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="D68" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="E68" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="F68" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -5280,10 +5280,10 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="D69" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E69" t="n">
         <v>0.8</v>
@@ -5351,7 +5351,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="D70" t="n">
         <v>0.5</v>
@@ -5422,10 +5422,10 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D71" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E71" t="n">
         <v>0.8</v>
@@ -5493,16 +5493,16 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="D72" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="E72" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="F72" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -5564,16 +5564,16 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="D73" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E73" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F73" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -5641,10 +5641,10 @@
         <v>0.6</v>
       </c>
       <c r="E74" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="F74" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -5706,16 +5706,16 @@
         </is>
       </c>
       <c r="C75" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E75" t="n">
         <v>0.6</v>
       </c>
-      <c r="D75" t="n">
+      <c r="F75" t="n">
         <v>0.6</v>
-      </c>
-      <c r="E75" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F75" t="n">
-        <v>0.8</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -5777,13 +5777,13 @@
         </is>
       </c>
       <c r="C76" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E76" t="n">
         <v>0.6</v>
-      </c>
-      <c r="D76" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E76" t="n">
-        <v>0.8</v>
       </c>
       <c r="F76" t="n">
         <v>0.8</v>
@@ -5854,7 +5854,7 @@
         <v>0.2</v>
       </c>
       <c r="E77" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F77" t="n">
         <v>0.8</v>
@@ -5919,16 +5919,16 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="D78" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="E78" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F78" t="n">
         <v>0.9</v>
-      </c>
-      <c r="F78" t="n">
-        <v>0.8</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>0.8</v>
       </c>
       <c r="F79" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -6061,16 +6061,16 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="D80" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E80" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="F80" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -6132,16 +6132,16 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="D81" t="n">
         <v>0.2</v>
       </c>
       <c r="E81" t="n">
-        <v>0.55</v>
+        <v>0.8</v>
       </c>
       <c r="F81" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -6203,16 +6203,16 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="D82" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E82" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F82" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -6274,16 +6274,16 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="D83" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E83" t="n">
         <v>0.6</v>
       </c>
       <c r="F83" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>0.5</v>
       </c>
       <c r="F84" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -6422,10 +6422,10 @@
         <v>0.2</v>
       </c>
       <c r="E85" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F85" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -6487,16 +6487,16 @@
         </is>
       </c>
       <c r="C86" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F86" t="n">
         <v>0.6</v>
-      </c>
-      <c r="D86" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E86" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F86" t="n">
-        <v>0.8</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -6558,16 +6558,16 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="D87" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E87" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="F87" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -6635,10 +6635,10 @@
         <v>0.2</v>
       </c>
       <c r="E88" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F88" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -6700,16 +6700,16 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D89" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E89" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="F89" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -6771,10 +6771,10 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D90" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E90" t="n">
         <v>0.8</v>
@@ -6842,13 +6842,13 @@
         </is>
       </c>
       <c r="C91" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E91" t="n">
         <v>0.6</v>
-      </c>
-      <c r="D91" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E91" t="n">
-        <v>0.7</v>
       </c>
       <c r="F91" t="n">
         <v>0.8</v>
@@ -6919,10 +6919,10 @@
         <v>0.5</v>
       </c>
       <c r="E92" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F92" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -6990,10 +6990,10 @@
         <v>0.5</v>
       </c>
       <c r="E93" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F93" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>0.5</v>
       </c>
       <c r="E94" t="n">
-        <v>0.7</v>
+        <v>0.55</v>
       </c>
       <c r="F94" t="n">
         <v>0.8</v>
@@ -7126,13 +7126,13 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="D95" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E95" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="F95" t="n">
         <v>0.8</v>
@@ -7197,13 +7197,13 @@
         </is>
       </c>
       <c r="C96" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E96" t="n">
         <v>0.4</v>
-      </c>
-      <c r="D96" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E96" t="n">
-        <v>0.7</v>
       </c>
       <c r="F96" t="n">
         <v>0.5</v>
@@ -7268,16 +7268,16 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D97" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E97" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="F97" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -7339,16 +7339,16 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="D98" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E98" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F98" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="D99" t="n">
         <v>0.5</v>
@@ -7481,16 +7481,16 @@
         </is>
       </c>
       <c r="C100" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E100" t="n">
         <v>0.6</v>
       </c>
-      <c r="D100" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E100" t="n">
+      <c r="F100" t="n">
         <v>0.7</v>
-      </c>
-      <c r="F100" t="n">
-        <v>0.8</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -7552,10 +7552,10 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D101" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E101" t="n">
         <v>0.8</v>
@@ -7623,16 +7623,16 @@
         </is>
       </c>
       <c r="C102" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E102" t="n">
         <v>0.6</v>
       </c>
-      <c r="D102" t="n">
+      <c r="F102" t="n">
         <v>0.6</v>
-      </c>
-      <c r="E102" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F102" t="n">
-        <v>0.8</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -7768,13 +7768,13 @@
         <v>0.2</v>
       </c>
       <c r="D104" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="E104" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="F104" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         <v>0.5</v>
       </c>
       <c r="F105" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D107" t="n">
         <v>0.5</v>
@@ -7987,7 +7987,7 @@
         <v>0.8</v>
       </c>
       <c r="F107" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -8049,13 +8049,13 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="D108" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E108" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F108" t="n">
         <v>0.9</v>
@@ -8126,7 +8126,7 @@
         <v>0.9</v>
       </c>
       <c r="E109" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F109" t="n">
         <v>0.9</v>
@@ -8194,13 +8194,13 @@
         <v>0.6</v>
       </c>
       <c r="D110" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E110" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="F110" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -8268,10 +8268,10 @@
         <v>0.6</v>
       </c>
       <c r="E111" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="F111" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -8333,16 +8333,16 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D112" t="n">
         <v>0.5</v>
       </c>
       <c r="E112" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="F112" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -8404,16 +8404,16 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D113" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E113" t="n">
         <v>0.8</v>
       </c>
       <c r="F113" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -8549,13 +8549,13 @@
         <v>0.6</v>
       </c>
       <c r="D115" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E115" t="n">
         <v>0.8</v>
       </c>
       <c r="F115" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>0.5</v>
       </c>
       <c r="E116" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F116" t="n">
         <v>0.8</v>
@@ -8697,7 +8697,7 @@
         <v>0.8</v>
       </c>
       <c r="F117" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D118" t="n">
         <v>0.5</v>
@@ -8768,7 +8768,7 @@
         <v>0.8</v>
       </c>
       <c r="F118" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -8830,16 +8830,16 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D119" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E119" t="n">
         <v>0.7</v>
       </c>
       <c r="F119" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -8904,10 +8904,10 @@
         <v>0.6</v>
       </c>
       <c r="D120" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E120" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F120" t="n">
         <v>0.8</v>
@@ -8975,7 +8975,7 @@
         <v>0.6</v>
       </c>
       <c r="D121" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E121" t="n">
         <v>0.8</v>
@@ -9052,7 +9052,7 @@
         <v>0.8</v>
       </c>
       <c r="F122" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D123" t="n">
         <v>0.5</v>
@@ -9123,7 +9123,7 @@
         <v>0.8</v>
       </c>
       <c r="F123" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -9185,13 +9185,13 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D124" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E124" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="F124" t="n">
         <v>0.8</v>
@@ -9256,16 +9256,16 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="D125" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E125" t="n">
         <v>0.8</v>
       </c>
       <c r="F125" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>0.2</v>
       </c>
       <c r="E126" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F126" t="n">
         <v>0.8</v>
@@ -9398,16 +9398,16 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="D127" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E127" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F127" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="C128" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E128" t="n">
         <v>0.5</v>
-      </c>
-      <c r="D128" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E128" t="n">
-        <v>0.6</v>
       </c>
       <c r="F128" t="n">
         <v>0.8</v>
@@ -9540,13 +9540,13 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D129" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E129" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="F129" t="n">
         <v>0.8</v>
@@ -9620,7 +9620,7 @@
         <v>0.2</v>
       </c>
       <c r="F130" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -9685,10 +9685,10 @@
         <v>0.6</v>
       </c>
       <c r="D131" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E131" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="F131" t="n">
         <v>0.8</v>
@@ -9753,16 +9753,16 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="D132" t="n">
-        <v>0.8</v>
+        <v>0.55</v>
       </c>
       <c r="E132" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F132" t="n">
         <v>0.6</v>
-      </c>
-      <c r="F132" t="n">
-        <v>0.9</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         <v>0.2</v>
       </c>
       <c r="F133" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -9895,13 +9895,13 @@
         </is>
       </c>
       <c r="C134" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E134" t="n">
         <v>0.6</v>
-      </c>
-      <c r="D134" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E134" t="n">
-        <v>0.8</v>
       </c>
       <c r="F134" t="n">
         <v>0.8</v>
@@ -9969,7 +9969,7 @@
         <v>0.6</v>
       </c>
       <c r="D135" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E135" t="n">
         <v>0.8</v>
@@ -10037,16 +10037,16 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="D136" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="E136" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F136" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
         <v>0.6</v>
       </c>
       <c r="D137" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E137" t="n">
         <v>0.7</v>
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="C138" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D138" t="n">
         <v>0.6</v>
       </c>
-      <c r="D138" t="n">
-        <v>0.7</v>
-      </c>
       <c r="E138" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F138" t="n">
         <v>0.9</v>
@@ -10250,13 +10250,13 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="D139" t="n">
         <v>0.5</v>
       </c>
       <c r="E139" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F139" t="n">
         <v>0.8</v>
@@ -10327,10 +10327,10 @@
         <v>0.5</v>
       </c>
       <c r="E140" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F140" t="n">
         <v>0.7</v>
-      </c>
-      <c r="F140" t="n">
-        <v>0.8</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
         <v>0.6</v>
       </c>
       <c r="D141" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E141" t="n">
         <v>0.8</v>
@@ -10463,7 +10463,7 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D142" t="n">
         <v>0.5</v>
@@ -10472,7 +10472,7 @@
         <v>0.8</v>
       </c>
       <c r="F142" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -10534,10 +10534,10 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D143" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E143" t="n">
         <v>0.8</v>
@@ -10605,16 +10605,16 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D144" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E144" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F144" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -10676,16 +10676,16 @@
         </is>
       </c>
       <c r="C145" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D145" t="n">
         <v>0.5</v>
       </c>
-      <c r="D145" t="n">
-        <v>0.3</v>
-      </c>
       <c r="E145" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F145" t="n">
         <v>0.6</v>
-      </c>
-      <c r="F145" t="n">
-        <v>0.8</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -10747,13 +10747,13 @@
         </is>
       </c>
       <c r="C146" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D146" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E146" t="n">
         <v>0.6</v>
-      </c>
-      <c r="D146" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E146" t="n">
-        <v>0.7</v>
       </c>
       <c r="F146" t="n">
         <v>0.8</v>
@@ -10818,7 +10818,7 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D147" t="n">
         <v>0.5</v>
@@ -10827,7 +10827,7 @@
         <v>0.8</v>
       </c>
       <c r="F147" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -10960,13 +10960,13 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="D149" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="E149" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="F149" t="n">
         <v>0.8</v>
@@ -11031,16 +11031,16 @@
         </is>
       </c>
       <c r="C150" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D150" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E150" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F150" t="n">
         <v>0.5</v>
-      </c>
-      <c r="D150" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E150" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F150" t="n">
-        <v>0.7</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -11102,16 +11102,16 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="D151" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="E151" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F151" t="n">
         <v>0.5</v>
-      </c>
-      <c r="F151" t="n">
-        <v>0.9</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -11173,16 +11173,16 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="D152" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E152" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F152" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
@@ -11247,13 +11247,13 @@
         <v>0.6</v>
       </c>
       <c r="D153" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E153" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F153" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -11315,16 +11315,16 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="D154" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E154" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F154" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -11395,7 +11395,7 @@
         <v>0.9</v>
       </c>
       <c r="F155" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -11457,16 +11457,16 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D156" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E156" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="F156" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -11528,16 +11528,16 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="D157" t="n">
-        <v>0.55</v>
+        <v>0.9</v>
       </c>
       <c r="E157" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F157" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
         <v>0.8</v>
       </c>
       <c r="F158" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
@@ -11670,16 +11670,16 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D159" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E159" t="n">
         <v>0.8</v>
       </c>
       <c r="F159" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
@@ -11744,7 +11744,7 @@
         <v>0.6</v>
       </c>
       <c r="D160" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E160" t="n">
         <v>0.8</v>
@@ -11812,16 +11812,16 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D161" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E161" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="F161" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -11883,7 +11883,7 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D162" t="n">
         <v>0.5</v>
@@ -11892,7 +11892,7 @@
         <v>0.8</v>
       </c>
       <c r="F162" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
         <v>0.8</v>
       </c>
       <c r="F163" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -12025,16 +12025,16 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="D164" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="E164" t="n">
         <v>0.8</v>
       </c>
       <c r="F164" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -12096,13 +12096,13 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="D165" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E165" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F165" t="n">
         <v>0.9</v>
@@ -12167,16 +12167,16 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="D166" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="E166" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="F166" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -12238,16 +12238,16 @@
         </is>
       </c>
       <c r="C167" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D167" t="n">
         <v>0.6</v>
       </c>
-      <c r="D167" t="n">
-        <v>0.5</v>
-      </c>
       <c r="E167" t="n">
         <v>0.8</v>
       </c>
       <c r="F167" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
@@ -12309,16 +12309,16 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="D168" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="E168" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F168" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
@@ -12389,7 +12389,7 @@
         <v>0.8</v>
       </c>
       <c r="F169" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="D170" t="n">
         <v>0.5</v>
@@ -12460,7 +12460,7 @@
         <v>0.8</v>
       </c>
       <c r="F170" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
@@ -12528,7 +12528,7 @@
         <v>0.5</v>
       </c>
       <c r="E171" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="F171" t="n">
         <v>0.8</v>
@@ -12593,16 +12593,16 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="D172" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E172" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F172" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
@@ -12664,16 +12664,16 @@
         </is>
       </c>
       <c r="C173" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D173" t="n">
         <v>0.4</v>
       </c>
-      <c r="D173" t="n">
-        <v>0.3</v>
-      </c>
       <c r="E173" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F173" t="n">
         <v>0.5</v>
-      </c>
-      <c r="F173" t="n">
-        <v>0.8</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D174" t="n">
         <v>0.5</v>
@@ -12806,13 +12806,13 @@
         </is>
       </c>
       <c r="C175" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D175" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E175" t="n">
         <v>0.4</v>
-      </c>
-      <c r="D175" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E175" t="n">
-        <v>0.5</v>
       </c>
       <c r="F175" t="n">
         <v>0.5</v>
@@ -12883,10 +12883,10 @@
         <v>0.5</v>
       </c>
       <c r="E176" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="F176" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
@@ -12948,13 +12948,13 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D177" t="n">
         <v>0.5</v>
       </c>
       <c r="E177" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="F177" t="n">
         <v>0.8</v>
@@ -13022,13 +13022,13 @@
         <v>0.6</v>
       </c>
       <c r="D178" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E178" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F178" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         <v>0.8</v>
       </c>
       <c r="F180" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
@@ -13232,16 +13232,16 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="D181" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E181" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="F181" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
@@ -13306,13 +13306,13 @@
         <v>0.6</v>
       </c>
       <c r="D182" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E182" t="n">
         <v>0.7</v>
       </c>
       <c r="F182" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D183" t="n">
         <v>0.5</v>
@@ -13383,7 +13383,7 @@
         <v>0.8</v>
       </c>
       <c r="F183" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
@@ -13445,10 +13445,10 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D184" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E184" t="n">
         <v>0.8</v>
@@ -13516,13 +13516,13 @@
         </is>
       </c>
       <c r="C185" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D185" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E185" t="n">
         <v>0.6</v>
-      </c>
-      <c r="D185" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E185" t="n">
-        <v>0.7</v>
       </c>
       <c r="F185" t="n">
         <v>0.8</v>
@@ -13587,7 +13587,7 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D186" t="n">
         <v>0.5</v>
@@ -13667,7 +13667,7 @@
         <v>0.8</v>
       </c>
       <c r="F187" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
@@ -13735,10 +13735,10 @@
         <v>0.2</v>
       </c>
       <c r="E188" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="F188" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D191" t="n">
         <v>0.5</v>
@@ -14084,7 +14084,7 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D193" t="n">
         <v>0.5</v>
@@ -14155,7 +14155,7 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="D194" t="n">
         <v>0.7</v>
@@ -14229,13 +14229,13 @@
         <v>0.6</v>
       </c>
       <c r="D195" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="E195" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="F195" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
@@ -14300,13 +14300,13 @@
         <v>0.6</v>
       </c>
       <c r="D196" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E196" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F196" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
@@ -14374,7 +14374,7 @@
         <v>0.2</v>
       </c>
       <c r="E197" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F197" t="n">
         <v>0.8</v>
@@ -14587,10 +14587,10 @@
         <v>0.5</v>
       </c>
       <c r="E200" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F200" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
@@ -14652,13 +14652,13 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D201" t="n">
         <v>0.5</v>
       </c>
       <c r="E201" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F201" t="n">
         <v>0.8</v>
@@ -14729,10 +14729,10 @@
         <v>0.5</v>
       </c>
       <c r="E202" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="F202" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
@@ -14800,10 +14800,10 @@
         <v>0.2</v>
       </c>
       <c r="E203" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="F203" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
@@ -14871,7 +14871,7 @@
         <v>0.2</v>
       </c>
       <c r="E204" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="F204" t="n">
         <v>0.8</v>
@@ -14945,7 +14945,7 @@
         <v>0.8</v>
       </c>
       <c r="F205" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
@@ -15007,7 +15007,7 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D206" t="n">
         <v>0.5</v>
@@ -15016,7 +15016,7 @@
         <v>0.8</v>
       </c>
       <c r="F206" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
@@ -15149,13 +15149,13 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D208" t="n">
         <v>0.5</v>
       </c>
       <c r="E208" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F208" t="n">
         <v>0.8</v>
@@ -15220,16 +15220,16 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D209" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E209" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F209" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
@@ -15291,13 +15291,13 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D210" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E210" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F210" t="n">
         <v>0.8</v>
@@ -15371,7 +15371,7 @@
         <v>0.6</v>
       </c>
       <c r="F211" t="n">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
@@ -15433,13 +15433,13 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D212" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E212" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F212" t="n">
         <v>0.9</v>
@@ -15506,16 +15506,16 @@
         </is>
       </c>
       <c r="C213" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D213" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E213" t="n">
         <v>0.9</v>
       </c>
-      <c r="D213" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E213" t="n">
-        <v>0.8</v>
-      </c>
       <c r="F213" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
@@ -15579,16 +15579,16 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="D214" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="E214" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="F214" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
@@ -15652,16 +15652,16 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="D215" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="E215" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="F215" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
@@ -15731,10 +15731,10 @@
         <v>0.6</v>
       </c>
       <c r="E216" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F216" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
@@ -15798,13 +15798,13 @@
         </is>
       </c>
       <c r="C217" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D217" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E217" t="n">
         <v>0.5</v>
-      </c>
-      <c r="D217" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E217" t="n">
-        <v>0.8</v>
       </c>
       <c r="F217" t="n">
         <v>0.6</v>
@@ -15871,13 +15871,13 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="D218" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="E218" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="F218" t="n">
         <v>0.7</v>
@@ -15953,7 +15953,7 @@
         <v>0.8</v>
       </c>
       <c r="F219" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
@@ -16023,10 +16023,10 @@
         <v>0.6</v>
       </c>
       <c r="E220" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F220" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
@@ -16090,16 +16090,16 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D221" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E221" t="n">
         <v>0.8</v>
       </c>
       <c r="F221" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
@@ -16169,10 +16169,10 @@
         <v>1</v>
       </c>
       <c r="E222" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="F222" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
@@ -16236,16 +16236,16 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D223" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E223" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="F223" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
@@ -16309,16 +16309,16 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="D224" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E224" t="n">
-        <v>0.6</v>
+        <v>0.85</v>
       </c>
       <c r="F224" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
@@ -16388,10 +16388,10 @@
         <v>0.5</v>
       </c>
       <c r="E225" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F225" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="D226" t="n">
         <v>0.5</v>
@@ -16528,16 +16528,16 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="D227" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E227" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F227" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
@@ -16607,10 +16607,10 @@
         <v>0.6</v>
       </c>
       <c r="E228" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F228" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
@@ -16674,16 +16674,16 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="D229" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E229" t="n">
         <v>0.8</v>
       </c>
       <c r="F229" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
@@ -16747,16 +16747,16 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="D230" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="E230" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="F230" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
@@ -16820,16 +16820,16 @@
         </is>
       </c>
       <c r="C231" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D231" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E231" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="F231" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
@@ -16966,13 +16966,13 @@
         </is>
       </c>
       <c r="C233" t="n">
+        <v>1</v>
+      </c>
+      <c r="D233" t="n">
+        <v>1</v>
+      </c>
+      <c r="E233" t="n">
         <v>0.9</v>
-      </c>
-      <c r="D233" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E233" t="n">
-        <v>0.8</v>
       </c>
       <c r="F233" t="n">
         <v>0.7</v>
@@ -17039,10 +17039,10 @@
         </is>
       </c>
       <c r="C234" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="D234" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="E234" t="n">
         <v>0.8</v>
@@ -17118,10 +17118,10 @@
         <v>0.5</v>
       </c>
       <c r="E235" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F235" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
@@ -17191,10 +17191,10 @@
         <v>0.9</v>
       </c>
       <c r="E236" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F236" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
@@ -17258,16 +17258,16 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="D237" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="E237" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="F237" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
@@ -17340,7 +17340,7 @@
         <v>0.5</v>
       </c>
       <c r="F238" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="G238" t="inlineStr">
         <is>
@@ -17404,16 +17404,16 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="D239" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="E239" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F239" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="G239" t="inlineStr">
         <is>
@@ -17477,16 +17477,16 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D240" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E240" t="n">
         <v>0.5</v>
       </c>
       <c r="F240" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
@@ -17550,16 +17550,16 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="D241" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="E241" t="n">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="F241" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
@@ -17623,16 +17623,16 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D242" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E242" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F242" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
@@ -17696,16 +17696,16 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="D243" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E243" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F243" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
@@ -17769,16 +17769,16 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="D244" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="E244" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F244" t="n">
         <v>0.7</v>
-      </c>
-      <c r="F244" t="n">
-        <v>0.5</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
@@ -17842,16 +17842,16 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D245" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="E245" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="F245" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
@@ -17924,7 +17924,7 @@
         <v>0.8</v>
       </c>
       <c r="F246" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G246" t="inlineStr">
         <is>
@@ -17988,16 +17988,16 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="D247" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E247" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F247" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G247" t="inlineStr">
         <is>
@@ -18067,10 +18067,10 @@
         <v>0.9</v>
       </c>
       <c r="E248" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F248" t="n">
         <v>0.7</v>
-      </c>
-      <c r="F248" t="n">
-        <v>0.6</v>
       </c>
       <c r="G248" t="inlineStr">
         <is>
@@ -18140,10 +18140,10 @@
         <v>1</v>
       </c>
       <c r="E249" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F249" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="G249" t="inlineStr">
         <is>
@@ -18213,10 +18213,10 @@
         <v>0.5</v>
       </c>
       <c r="E250" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="F250" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G250" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>1</v>
       </c>
       <c r="E251" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F251" t="n">
         <v>0.7</v>
@@ -18359,10 +18359,10 @@
         <v>0.5</v>
       </c>
       <c r="E252" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F252" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="G252" t="inlineStr">
         <is>
@@ -18426,16 +18426,16 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="D253" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="E253" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="F253" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="G253" t="inlineStr">
         <is>
@@ -18505,10 +18505,10 @@
         <v>1</v>
       </c>
       <c r="E254" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F254" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="G254" t="inlineStr">
         <is>
@@ -18651,10 +18651,10 @@
         <v>0.2</v>
       </c>
       <c r="E256" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F256" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G256" t="inlineStr">
         <is>
@@ -18724,10 +18724,10 @@
         <v>1</v>
       </c>
       <c r="E257" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="F257" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="G257" t="inlineStr">
         <is>
@@ -18864,16 +18864,16 @@
         </is>
       </c>
       <c r="C259" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="D259" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E259" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="F259" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="G259" t="inlineStr">
         <is>
@@ -18937,7 +18937,7 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D260" t="n">
         <v>0.5</v>
@@ -18946,7 +18946,7 @@
         <v>0.8</v>
       </c>
       <c r="F260" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="G260" t="inlineStr">
         <is>
@@ -19010,13 +19010,13 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="D261" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="E261" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="F261" t="n">
         <v>0.5</v>
@@ -19083,16 +19083,16 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="D262" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="E262" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F262" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="G262" t="inlineStr">
         <is>
@@ -19302,13 +19302,13 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="D265" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E265" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F265" t="n">
         <v>0.5</v>
@@ -19375,16 +19375,16 @@
         </is>
       </c>
       <c r="C266" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D266" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E266" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F266" t="n">
         <v>0.5</v>
-      </c>
-      <c r="D266" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E266" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F266" t="n">
-        <v>0.6</v>
       </c>
       <c r="G266" t="inlineStr">
         <is>
@@ -19448,16 +19448,16 @@
         </is>
       </c>
       <c r="C267" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="D267" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="E267" t="n">
         <v>0.6</v>
       </c>
       <c r="F267" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G267" t="inlineStr">
         <is>
@@ -19521,16 +19521,16 @@
         </is>
       </c>
       <c r="C268" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="D268" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="E268" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F268" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="G268" t="inlineStr">
         <is>
@@ -19594,16 +19594,16 @@
         </is>
       </c>
       <c r="C269" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D269" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E269" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F269" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="G269" t="inlineStr">
         <is>
@@ -19676,7 +19676,7 @@
         <v>0.5</v>
       </c>
       <c r="F270" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G270" t="inlineStr">
         <is>
@@ -19740,16 +19740,16 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>0.2</v>
+        <v>0.55</v>
       </c>
       <c r="D271" t="n">
-        <v>0.2</v>
+        <v>0.55</v>
       </c>
       <c r="E271" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="F271" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="G271" t="inlineStr">
         <is>
@@ -19822,7 +19822,7 @@
         <v>0.8</v>
       </c>
       <c r="F272" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -19886,16 +19886,16 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D273" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E273" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="F273" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -19959,16 +19959,16 @@
         </is>
       </c>
       <c r="C274" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="D274" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E274" t="n">
         <v>0.6</v>
       </c>
       <c r="F274" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -20032,16 +20032,16 @@
         </is>
       </c>
       <c r="C275" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D275" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E275" t="n">
         <v>0.9</v>
       </c>
       <c r="F275" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -20105,16 +20105,16 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D276" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E276" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F276" t="n">
         <v>0.5</v>
-      </c>
-      <c r="F276" t="n">
-        <v>0.2</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -20178,10 +20178,10 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="D277" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E277" t="n">
         <v>0.8</v>
@@ -20257,7 +20257,7 @@
         <v>0.8</v>
       </c>
       <c r="E278" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="F278" t="n">
         <v>0.6</v>
@@ -20324,13 +20324,13 @@
         </is>
       </c>
       <c r="C279" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D279" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E279" t="n">
         <v>0.5</v>
-      </c>
-      <c r="D279" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E279" t="n">
-        <v>0.6</v>
       </c>
       <c r="F279" t="n">
         <v>0.6</v>
@@ -20397,16 +20397,16 @@
         </is>
       </c>
       <c r="C280" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D280" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E280" t="n">
         <v>0.9</v>
       </c>
-      <c r="D280" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="E280" t="n">
-        <v>0.8</v>
-      </c>
       <c r="F280" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -20470,16 +20470,16 @@
         </is>
       </c>
       <c r="C281" t="n">
+        <v>1</v>
+      </c>
+      <c r="D281" t="n">
+        <v>1</v>
+      </c>
+      <c r="E281" t="n">
+        <v>1</v>
+      </c>
+      <c r="F281" t="n">
         <v>0.9</v>
-      </c>
-      <c r="D281" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E281" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F281" t="n">
-        <v>0.6</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -20543,16 +20543,16 @@
         </is>
       </c>
       <c r="C282" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D282" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E282" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="F282" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="G282" t="inlineStr">
         <is>
@@ -20616,13 +20616,13 @@
         </is>
       </c>
       <c r="C283" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="D283" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E283" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F283" t="n">
         <v>0.6</v>
@@ -20695,7 +20695,7 @@
         <v>0.9</v>
       </c>
       <c r="E284" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="F284" t="n">
         <v>0.9</v>
@@ -20762,16 +20762,16 @@
         </is>
       </c>
       <c r="C285" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D285" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E285" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F285" t="n">
         <v>0.6</v>
-      </c>
-      <c r="D285" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E285" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F285" t="n">
-        <v>0.7</v>
       </c>
       <c r="G285" t="inlineStr">
         <is>
@@ -20841,7 +20841,7 @@
         <v>0.2</v>
       </c>
       <c r="E286" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F286" t="n">
         <v>0.5</v>
@@ -20908,16 +20908,16 @@
         </is>
       </c>
       <c r="C287" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="D287" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="E287" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="F287" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="G287" t="inlineStr">
         <is>
@@ -20981,16 +20981,16 @@
         </is>
       </c>
       <c r="C288" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D288" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E288" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F288" t="n">
         <v>0.5</v>
-      </c>
-      <c r="D288" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E288" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F288" t="n">
-        <v>0.6</v>
       </c>
       <c r="G288" t="inlineStr">
         <is>
@@ -21127,10 +21127,10 @@
         </is>
       </c>
       <c r="C290" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D290" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E290" t="n">
         <v>0.8</v>
@@ -21200,16 +21200,16 @@
         </is>
       </c>
       <c r="C291" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="D291" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="E291" t="n">
         <v>0.6</v>
       </c>
       <c r="F291" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G291" t="inlineStr">
         <is>
@@ -21273,16 +21273,16 @@
         </is>
       </c>
       <c r="C292" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D292" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E292" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F292" t="n">
         <v>0.6</v>
-      </c>
-      <c r="D292" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E292" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F292" t="n">
-        <v>0.9</v>
       </c>
       <c r="G292" t="inlineStr">
         <is>
@@ -21352,10 +21352,10 @@
         <v>0.9</v>
       </c>
       <c r="E293" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F293" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="G293" t="inlineStr">
         <is>
@@ -21419,16 +21419,16 @@
         </is>
       </c>
       <c r="C294" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D294" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E294" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F294" t="n">
         <v>0.6</v>
-      </c>
-      <c r="D294" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E294" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F294" t="n">
-        <v>0.7</v>
       </c>
       <c r="G294" t="inlineStr">
         <is>
@@ -21498,10 +21498,10 @@
         <v>0.2</v>
       </c>
       <c r="E295" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="F295" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="G295" t="inlineStr">
         <is>
@@ -21565,16 +21565,16 @@
         </is>
       </c>
       <c r="C296" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="D296" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="E296" t="n">
-        <v>0.6</v>
+        <v>0.85</v>
       </c>
       <c r="F296" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="G296" t="inlineStr">
         <is>
@@ -21644,10 +21644,10 @@
         <v>0.9</v>
       </c>
       <c r="E297" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F297" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G297" t="inlineStr">
         <is>
@@ -21711,16 +21711,16 @@
         </is>
       </c>
       <c r="C298" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D298" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E298" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F298" t="n">
         <v>0.5</v>
-      </c>
-      <c r="D298" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E298" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F298" t="n">
-        <v>0.6</v>
       </c>
       <c r="G298" t="inlineStr">
         <is>
@@ -21784,16 +21784,16 @@
         </is>
       </c>
       <c r="C299" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="D299" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="E299" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="F299" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="G299" t="inlineStr">
         <is>
@@ -21860,13 +21860,13 @@
         <v>0.5</v>
       </c>
       <c r="D300" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E300" t="n">
         <v>0.8</v>
       </c>
       <c r="F300" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="G300" t="inlineStr">
         <is>
@@ -21930,16 +21930,16 @@
         </is>
       </c>
       <c r="C301" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="D301" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="E301" t="n">
         <v>0.9</v>
       </c>
       <c r="F301" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="G301" t="inlineStr">
         <is>
@@ -22009,10 +22009,10 @@
         <v>0.9</v>
       </c>
       <c r="E302" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F302" t="n">
         <v>0.6</v>
-      </c>
-      <c r="F302" t="n">
-        <v>0.5</v>
       </c>
       <c r="G302" t="inlineStr">
         <is>
@@ -22082,10 +22082,10 @@
         <v>1</v>
       </c>
       <c r="E303" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="F303" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="G303" t="inlineStr">
         <is>
@@ -22158,7 +22158,7 @@
         <v>0.6</v>
       </c>
       <c r="F304" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="G304" t="inlineStr">
         <is>
@@ -22231,7 +22231,7 @@
         <v>0.8</v>
       </c>
       <c r="F305" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="G305" t="inlineStr">
         <is>
@@ -22304,7 +22304,7 @@
         <v>0.6</v>
       </c>
       <c r="F306" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G306" t="inlineStr">
         <is>
@@ -22368,16 +22368,16 @@
         </is>
       </c>
       <c r="C307" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D307" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E307" t="n">
         <v>0.6</v>
       </c>
-      <c r="D307" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E307" t="n">
-        <v>0.5</v>
-      </c>
       <c r="F307" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G307" t="inlineStr">
         <is>
@@ -22447,7 +22447,7 @@
         <v>0.9</v>
       </c>
       <c r="E308" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F308" t="n">
         <v>0.6</v>
@@ -22514,16 +22514,16 @@
         </is>
       </c>
       <c r="C309" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D309" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E309" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="F309" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G309" t="inlineStr">
         <is>
@@ -22593,7 +22593,7 @@
         <v>0.2</v>
       </c>
       <c r="E310" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="F310" t="n">
         <v>0.6</v>
@@ -22666,10 +22666,10 @@
         <v>1</v>
       </c>
       <c r="E311" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="F311" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G311" t="inlineStr">
         <is>
@@ -22739,10 +22739,10 @@
         <v>1</v>
       </c>
       <c r="E312" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="F312" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="G312" t="inlineStr">
         <is>
@@ -22806,16 +22806,16 @@
         </is>
       </c>
       <c r="C313" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D313" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E313" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F313" t="n">
         <v>0.6</v>
-      </c>
-      <c r="D313" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E313" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F313" t="n">
-        <v>0.7</v>
       </c>
       <c r="G313" t="inlineStr">
         <is>
@@ -22888,7 +22888,7 @@
         <v>0.8</v>
       </c>
       <c r="F314" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G314" t="inlineStr">
         <is>
@@ -22961,7 +22961,7 @@
         <v>1</v>
       </c>
       <c r="F315" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="G315" t="inlineStr">
         <is>
@@ -23025,16 +23025,16 @@
         </is>
       </c>
       <c r="C316" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="D316" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E316" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="F316" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="G316" t="inlineStr">
         <is>
@@ -23104,10 +23104,10 @@
         <v>0.2</v>
       </c>
       <c r="E317" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F317" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="G317" t="inlineStr">
         <is>
@@ -23171,16 +23171,16 @@
         </is>
       </c>
       <c r="C318" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D318" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E318" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="F318" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="G318" t="inlineStr">
         <is>
@@ -23244,16 +23244,16 @@
         </is>
       </c>
       <c r="C319" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="D319" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="E319" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F319" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G319" t="inlineStr">
         <is>
@@ -23317,13 +23317,13 @@
         </is>
       </c>
       <c r="C320" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D320" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E320" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F320" t="n">
         <v>0.5</v>
@@ -23390,16 +23390,16 @@
         </is>
       </c>
       <c r="C321" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="D321" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="E321" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="F321" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="G321" t="inlineStr">
         <is>
@@ -23463,16 +23463,16 @@
         </is>
       </c>
       <c r="C322" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D322" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E322" t="n">
         <v>0.6</v>
       </c>
-      <c r="D322" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E322" t="n">
-        <v>0.8</v>
-      </c>
       <c r="F322" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="G322" t="inlineStr">
         <is>
@@ -23536,16 +23536,16 @@
         </is>
       </c>
       <c r="C323" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D323" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E323" t="n">
         <v>0.5</v>
       </c>
       <c r="F323" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="G323" t="inlineStr">
         <is>
@@ -23688,10 +23688,10 @@
         <v>0.6</v>
       </c>
       <c r="E325" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F325" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G325" t="inlineStr">
         <is>
@@ -23755,16 +23755,16 @@
         </is>
       </c>
       <c r="C326" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D326" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E326" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F326" t="n">
         <v>0.5</v>
-      </c>
-      <c r="D326" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E326" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F326" t="n">
-        <v>0.8</v>
       </c>
       <c r="G326" t="inlineStr">
         <is>
@@ -23834,10 +23834,10 @@
         <v>0.2</v>
       </c>
       <c r="E327" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F327" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G327" t="inlineStr">
         <is>
@@ -23901,16 +23901,16 @@
         </is>
       </c>
       <c r="C328" t="n">
-        <v>0.5</v>
+        <v>0.95</v>
       </c>
       <c r="D328" t="n">
-        <v>0.5</v>
+        <v>0.95</v>
       </c>
       <c r="E328" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="F328" t="n">
-        <v>0.6</v>
+        <v>0.95</v>
       </c>
       <c r="G328" t="inlineStr">
         <is>
@@ -23974,16 +23974,16 @@
         </is>
       </c>
       <c r="C329" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D329" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E329" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="F329" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="G329" t="inlineStr">
         <is>
@@ -24047,16 +24047,16 @@
         </is>
       </c>
       <c r="C330" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D330" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E330" t="n">
         <v>0.6</v>
       </c>
-      <c r="D330" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E330" t="n">
-        <v>0.8</v>
-      </c>
       <c r="F330" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G330" t="inlineStr">
         <is>
@@ -24120,10 +24120,10 @@
         </is>
       </c>
       <c r="C331" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="D331" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="E331" t="n">
         <v>0.9</v>
@@ -24193,16 +24193,16 @@
         </is>
       </c>
       <c r="C332" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D332" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E332" t="n">
         <v>0.6</v>
       </c>
-      <c r="D332" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E332" t="n">
-        <v>0.8</v>
-      </c>
       <c r="F332" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G332" t="inlineStr">
         <is>
@@ -24272,10 +24272,10 @@
         <v>0.9</v>
       </c>
       <c r="E333" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F333" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="G333" t="inlineStr">
         <is>
@@ -24339,16 +24339,16 @@
         </is>
       </c>
       <c r="C334" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D334" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E334" t="n">
         <v>0.6</v>
       </c>
-      <c r="D334" t="n">
+      <c r="F334" t="n">
         <v>0.6</v>
-      </c>
-      <c r="E334" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F334" t="n">
-        <v>0.7</v>
       </c>
       <c r="G334" t="inlineStr">
         <is>
@@ -24418,10 +24418,10 @@
         <v>0.9</v>
       </c>
       <c r="E335" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F335" t="n">
         <v>0.6</v>
-      </c>
-      <c r="F335" t="n">
-        <v>0.5</v>
       </c>
       <c r="G335" t="inlineStr">
         <is>
@@ -24491,7 +24491,7 @@
         <v>0.2</v>
       </c>
       <c r="E336" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F336" t="n">
         <v>0.6</v>
@@ -24558,16 +24558,16 @@
         </is>
       </c>
       <c r="C337" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="D337" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="E337" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="F337" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G337" t="inlineStr">
         <is>
@@ -24631,16 +24631,16 @@
         </is>
       </c>
       <c r="C338" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D338" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E338" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F338" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="G338" t="inlineStr">
         <is>
@@ -24710,10 +24710,10 @@
         <v>0.9</v>
       </c>
       <c r="E339" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F339" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="G339" t="inlineStr">
         <is>
@@ -24777,16 +24777,16 @@
         </is>
       </c>
       <c r="C340" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D340" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E340" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="F340" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G340" t="inlineStr">
         <is>
@@ -24923,16 +24923,16 @@
         </is>
       </c>
       <c r="C342" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D342" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E342" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F342" t="n">
         <v>0.6</v>
-      </c>
-      <c r="D342" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E342" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F342" t="n">
-        <v>0.8</v>
       </c>
       <c r="G342" t="inlineStr">
         <is>
@@ -25005,7 +25005,7 @@
         <v>0.5</v>
       </c>
       <c r="F343" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="G343" t="inlineStr">
         <is>
@@ -25069,16 +25069,16 @@
         </is>
       </c>
       <c r="C344" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D344" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E344" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="F344" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G344" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>1</v>
       </c>
       <c r="E345" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="F345" t="n">
         <v>0.7</v>
@@ -25221,10 +25221,10 @@
         <v>0.2</v>
       </c>
       <c r="E346" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="F346" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G346" t="inlineStr">
         <is>
@@ -25288,16 +25288,16 @@
         </is>
       </c>
       <c r="C347" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D347" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E347" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F347" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G347" t="inlineStr">
         <is>
@@ -25367,10 +25367,10 @@
         <v>0.6</v>
       </c>
       <c r="E348" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="F348" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="G348" t="inlineStr">
         <is>
@@ -25434,16 +25434,16 @@
         </is>
       </c>
       <c r="C349" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D349" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E349" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F349" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="G349" t="inlineStr">
         <is>
@@ -25507,16 +25507,16 @@
         </is>
       </c>
       <c r="C350" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="D350" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="E350" t="n">
-        <v>0.7</v>
+        <v>0.88</v>
       </c>
       <c r="F350" t="n">
-        <v>0.6</v>
+        <v>0.83</v>
       </c>
       <c r="G350" t="inlineStr">
         <is>
@@ -25586,10 +25586,10 @@
         <v>0.5</v>
       </c>
       <c r="E351" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="F351" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G351" t="inlineStr">
         <is>
@@ -25653,16 +25653,16 @@
         </is>
       </c>
       <c r="C352" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="D352" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="E352" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="F352" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="G352" t="inlineStr">
         <is>
@@ -25726,16 +25726,16 @@
         </is>
       </c>
       <c r="C353" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D353" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E353" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="F353" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="G353" t="inlineStr">
         <is>
@@ -25799,16 +25799,16 @@
         </is>
       </c>
       <c r="C354" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D354" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E354" t="n">
         <v>0.6</v>
       </c>
-      <c r="D354" t="n">
+      <c r="F354" t="n">
         <v>0.6</v>
-      </c>
-      <c r="E354" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F354" t="n">
-        <v>0.7</v>
       </c>
       <c r="G354" t="inlineStr">
         <is>
@@ -25872,16 +25872,16 @@
         </is>
       </c>
       <c r="C355" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D355" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E355" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="F355" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="G355" t="inlineStr">
         <is>
@@ -25945,16 +25945,16 @@
         </is>
       </c>
       <c r="C356" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="D356" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="E356" t="n">
         <v>0.8</v>
       </c>
       <c r="F356" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G356" t="inlineStr">
         <is>
@@ -26024,10 +26024,10 @@
         <v>0.9</v>
       </c>
       <c r="E357" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="F357" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="G357" t="inlineStr">
         <is>
@@ -26091,16 +26091,16 @@
         </is>
       </c>
       <c r="C358" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="D358" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E358" t="n">
         <v>0.6</v>
       </c>
       <c r="F358" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G358" t="inlineStr">
         <is>
@@ -26164,16 +26164,16 @@
         </is>
       </c>
       <c r="C359" t="n">
+        <v>1</v>
+      </c>
+      <c r="D359" t="n">
+        <v>1</v>
+      </c>
+      <c r="E359" t="n">
         <v>0.9</v>
       </c>
-      <c r="D359" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E359" t="n">
+      <c r="F359" t="n">
         <v>0.6</v>
-      </c>
-      <c r="F359" t="n">
-        <v>0.5</v>
       </c>
       <c r="G359" t="inlineStr">
         <is>
@@ -26243,10 +26243,10 @@
         <v>0.6</v>
       </c>
       <c r="E360" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="F360" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="G360" t="inlineStr">
         <is>
@@ -26316,10 +26316,10 @@
         <v>0.6</v>
       </c>
       <c r="E361" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F361" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="G361" t="inlineStr">
         <is>
@@ -26383,16 +26383,16 @@
         </is>
       </c>
       <c r="C362" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="D362" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E362" t="n">
         <v>0.5</v>
       </c>
-      <c r="E362" t="n">
-        <v>0.6</v>
-      </c>
       <c r="F362" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G362" t="inlineStr">
         <is>
@@ -26462,10 +26462,10 @@
         <v>0.2</v>
       </c>
       <c r="E363" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F363" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G363" t="inlineStr">
         <is>
@@ -26529,16 +26529,16 @@
         </is>
       </c>
       <c r="C364" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="D364" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E364" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F364" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="G364" t="inlineStr">
         <is>
@@ -26602,16 +26602,16 @@
         </is>
       </c>
       <c r="C365" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="D365" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E365" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="F365" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="G365" t="inlineStr">
         <is>
@@ -26675,16 +26675,16 @@
         </is>
       </c>
       <c r="C366" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D366" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E366" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="F366" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="G366" t="inlineStr">
         <is>
@@ -26748,16 +26748,16 @@
         </is>
       </c>
       <c r="C367" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D367" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E367" t="n">
         <v>0.6</v>
       </c>
-      <c r="D367" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E367" t="n">
-        <v>0.8</v>
-      </c>
       <c r="F367" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="G367" t="inlineStr">
         <is>
@@ -26827,10 +26827,10 @@
         <v>0.9</v>
       </c>
       <c r="E368" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="F368" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="G368" t="inlineStr">
         <is>
@@ -26900,10 +26900,10 @@
         <v>0.2</v>
       </c>
       <c r="E369" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F369" t="n">
         <v>0.5</v>
-      </c>
-      <c r="F369" t="n">
-        <v>0.6</v>
       </c>
       <c r="G369" t="inlineStr">
         <is>
@@ -26973,7 +26973,7 @@
         <v>0.6</v>
       </c>
       <c r="E370" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F370" t="n">
         <v>0.7</v>
@@ -27046,10 +27046,10 @@
         <v>0.9</v>
       </c>
       <c r="E371" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F371" t="n">
         <v>0.6</v>
-      </c>
-      <c r="F371" t="n">
-        <v>0.7</v>
       </c>
       <c r="G371" t="inlineStr">
         <is>
@@ -27113,16 +27113,16 @@
         </is>
       </c>
       <c r="C372" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="D372" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E372" t="n">
         <v>0.6</v>
       </c>
       <c r="F372" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="G372" t="inlineStr">
         <is>
@@ -27186,16 +27186,16 @@
         </is>
       </c>
       <c r="C373" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D373" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E373" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="F373" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="G373" t="inlineStr">
         <is>
@@ -27338,10 +27338,10 @@
         <v>0.2</v>
       </c>
       <c r="E375" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F375" t="n">
         <v>0.5</v>
-      </c>
-      <c r="F375" t="n">
-        <v>0.6</v>
       </c>
       <c r="G375" t="inlineStr">
         <is>
@@ -27405,13 +27405,13 @@
         </is>
       </c>
       <c r="C376" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="D376" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="E376" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="F376" t="n">
         <v>0.9</v>
@@ -27478,16 +27478,16 @@
         </is>
       </c>
       <c r="C377" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D377" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E377" t="n">
-        <v>0.95</v>
+        <v>0.6</v>
       </c>
       <c r="F377" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G377" t="inlineStr">
         <is>
@@ -27551,16 +27551,16 @@
         </is>
       </c>
       <c r="C378" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D378" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E378" t="n">
         <v>0.6</v>
       </c>
-      <c r="D378" t="n">
+      <c r="F378" t="n">
         <v>0.6</v>
-      </c>
-      <c r="E378" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F378" t="n">
-        <v>0.5</v>
       </c>
       <c r="G378" t="inlineStr">
         <is>
@@ -27630,10 +27630,10 @@
         <v>0.6</v>
       </c>
       <c r="E379" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F379" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G379" t="inlineStr">
         <is>
@@ -27697,16 +27697,16 @@
         </is>
       </c>
       <c r="C380" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="D380" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="E380" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="F380" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="G380" t="inlineStr">
         <is>
@@ -27770,16 +27770,16 @@
         </is>
       </c>
       <c r="C381" t="n">
-        <v>0.2</v>
+        <v>0.55</v>
       </c>
       <c r="D381" t="n">
-        <v>0.2</v>
+        <v>0.52</v>
       </c>
       <c r="E381" t="n">
         <v>0.8</v>
       </c>
       <c r="F381" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="G381" t="inlineStr">
         <is>
@@ -27843,16 +27843,16 @@
         </is>
       </c>
       <c r="C382" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="D382" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E382" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F382" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="G382" t="inlineStr">
         <is>
@@ -27916,16 +27916,16 @@
         </is>
       </c>
       <c r="C383" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="D383" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="E383" t="n">
         <v>0.8</v>
       </c>
       <c r="F383" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="G383" t="inlineStr">
         <is>
@@ -27998,7 +27998,7 @@
         <v>0.8</v>
       </c>
       <c r="F384" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="G384" t="inlineStr">
         <is>
@@ -28062,16 +28062,16 @@
         </is>
       </c>
       <c r="C385" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D385" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E385" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F385" t="n">
         <v>0.6</v>
-      </c>
-      <c r="D385" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E385" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F385" t="n">
-        <v>0.8</v>
       </c>
       <c r="G385" t="inlineStr">
         <is>
@@ -28135,16 +28135,16 @@
         </is>
       </c>
       <c r="C386" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="D386" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="E386" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F386" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G386" t="inlineStr">
         <is>
@@ -28208,16 +28208,16 @@
         </is>
       </c>
       <c r="C387" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D387" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E387" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F387" t="n">
         <v>0.5</v>
-      </c>
-      <c r="D387" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E387" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F387" t="n">
-        <v>0.7</v>
       </c>
       <c r="G387" t="inlineStr">
         <is>
@@ -28281,16 +28281,16 @@
         </is>
       </c>
       <c r="C388" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D388" t="n">
         <v>0.5</v>
       </c>
       <c r="E388" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F388" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="G388" t="inlineStr">
         <is>
@@ -28354,16 +28354,16 @@
         </is>
       </c>
       <c r="C389" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="D389" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="E389" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F389" t="n">
-        <v>0.85</v>
+        <v>0.6</v>
       </c>
       <c r="G389" t="inlineStr">
         <is>
@@ -28427,16 +28427,16 @@
         </is>
       </c>
       <c r="C390" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="D390" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="E390" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="F390" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="G390" t="inlineStr">
         <is>
@@ -28503,10 +28503,10 @@
         <v>0.9</v>
       </c>
       <c r="D391" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="E391" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="F391" t="n">
         <v>0.7</v>
@@ -28579,10 +28579,10 @@
         <v>0.9</v>
       </c>
       <c r="E392" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="F392" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G392" t="inlineStr">
         <is>
@@ -28646,16 +28646,16 @@
         </is>
       </c>
       <c r="C393" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="D393" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="E393" t="n">
         <v>0.7</v>
       </c>
       <c r="F393" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="G393" t="inlineStr">
         <is>
@@ -28719,16 +28719,16 @@
         </is>
       </c>
       <c r="C394" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="D394" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="E394" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="F394" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G394" t="inlineStr">
         <is>
@@ -28792,10 +28792,10 @@
         </is>
       </c>
       <c r="C395" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="D395" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="E395" t="n">
         <v>0.8</v>
@@ -28871,10 +28871,10 @@
         <v>0.5</v>
       </c>
       <c r="E396" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="F396" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G396" t="inlineStr">
         <is>
@@ -28938,10 +28938,10 @@
         </is>
       </c>
       <c r="C397" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="D397" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="E397" t="n">
         <v>0.9</v>
@@ -29011,16 +29011,16 @@
         </is>
       </c>
       <c r="C398" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D398" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E398" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F398" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="G398" t="inlineStr">
         <is>
@@ -29084,16 +29084,16 @@
         </is>
       </c>
       <c r="C399" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D399" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E399" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F399" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G399" t="inlineStr">
         <is>
@@ -29157,16 +29157,16 @@
         </is>
       </c>
       <c r="C400" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="D400" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="E400" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="F400" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="G400" t="inlineStr">
         <is>
@@ -29230,13 +29230,13 @@
         </is>
       </c>
       <c r="C401" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D401" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E401" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="F401" t="n">
         <v>0.6</v>
@@ -29303,16 +29303,16 @@
         </is>
       </c>
       <c r="C402" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D402" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E402" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F402" t="n">
         <v>0.4</v>
-      </c>
-      <c r="D402" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E402" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F402" t="n">
-        <v>0.7</v>
       </c>
       <c r="G402" t="inlineStr">
         <is>
@@ -29376,16 +29376,16 @@
         </is>
       </c>
       <c r="C403" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="D403" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="E403" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="F403" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="G403" t="inlineStr">
         <is>
@@ -29455,10 +29455,10 @@
         <v>0.9</v>
       </c>
       <c r="E404" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F404" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="G404" t="inlineStr">
         <is>
@@ -29528,10 +29528,10 @@
         <v>0.5</v>
       </c>
       <c r="E405" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="F405" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="G405" t="inlineStr">
         <is>
@@ -29601,10 +29601,10 @@
         <v>0.5</v>
       </c>
       <c r="E406" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F406" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G406" t="inlineStr">
         <is>
@@ -29677,7 +29677,7 @@
         <v>0.3</v>
       </c>
       <c r="F407" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G407" t="inlineStr">
         <is>
@@ -29749,10 +29749,10 @@
         <v>0.8</v>
       </c>
       <c r="E408" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="F408" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G408" t="inlineStr">
         <is>
@@ -29968,16 +29968,16 @@
         </is>
       </c>
       <c r="C411" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="D411" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E411" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F411" t="n">
         <v>0.5</v>
-      </c>
-      <c r="F411" t="n">
-        <v>0.7</v>
       </c>
       <c r="G411" t="inlineStr">
         <is>
@@ -30043,13 +30043,13 @@
         </is>
       </c>
       <c r="C412" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="D412" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E412" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F412" t="n">
         <v>0.9</v>
@@ -30127,7 +30127,7 @@
         <v>0.7</v>
       </c>
       <c r="F413" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G413" t="inlineStr">
         <is>
@@ -30193,13 +30193,13 @@
         </is>
       </c>
       <c r="C414" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D414" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E414" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F414" t="n">
         <v>0.9</v>
@@ -30343,10 +30343,10 @@
         </is>
       </c>
       <c r="C416" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="D416" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E416" t="n">
         <v>0.8</v>
@@ -30493,13 +30493,13 @@
         </is>
       </c>
       <c r="C418" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="D418" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E418" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F418" t="n">
         <v>0.9</v>
@@ -30574,10 +30574,10 @@
         <v>0.8</v>
       </c>
       <c r="E419" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="F419" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G419" t="inlineStr">
         <is>
@@ -30649,7 +30649,7 @@
         <v>0.9</v>
       </c>
       <c r="E420" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="F420" t="n">
         <v>0.8</v>
@@ -30724,7 +30724,7 @@
         <v>0.8</v>
       </c>
       <c r="E421" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F421" t="n">
         <v>0.9</v>
@@ -30802,7 +30802,7 @@
         <v>0.7</v>
       </c>
       <c r="F422" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="G422" t="inlineStr">
         <is>
@@ -30868,16 +30868,16 @@
         </is>
       </c>
       <c r="C423" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="D423" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E423" t="n">
         <v>0.7</v>
       </c>
       <c r="F423" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G423" t="inlineStr">
         <is>
@@ -31018,16 +31018,16 @@
         </is>
       </c>
       <c r="C425" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="D425" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="E425" t="n">
         <v>0.8</v>
       </c>
       <c r="F425" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G425" t="inlineStr">
         <is>
@@ -31099,7 +31099,7 @@
         <v>0.9</v>
       </c>
       <c r="E426" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F426" t="n">
         <v>0.8</v>
@@ -31168,13 +31168,13 @@
         </is>
       </c>
       <c r="C427" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="D427" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E427" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F427" t="n">
         <v>0.9</v>
@@ -31252,7 +31252,7 @@
         <v>0.3</v>
       </c>
       <c r="F428" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="G428" t="inlineStr">
         <is>
@@ -31327,7 +31327,7 @@
         <v>0.7</v>
       </c>
       <c r="F429" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="G429" t="inlineStr">
         <is>
@@ -31402,7 +31402,7 @@
         <v>0.9</v>
       </c>
       <c r="F430" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G430" t="inlineStr">
         <is>
@@ -31468,10 +31468,10 @@
         </is>
       </c>
       <c r="C431" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="D431" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="E431" t="n">
         <v>0.8</v>
@@ -31543,16 +31543,16 @@
         </is>
       </c>
       <c r="C432" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="D432" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E432" t="n">
         <v>0.5</v>
       </c>
       <c r="F432" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G432" t="inlineStr">
         <is>
@@ -31627,7 +31627,7 @@
         <v>0.7</v>
       </c>
       <c r="F433" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="G433" t="inlineStr">
         <is>
@@ -31699,10 +31699,10 @@
         <v>0.8</v>
       </c>
       <c r="E434" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="F434" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G434" t="inlineStr">
         <is>
@@ -31768,16 +31768,16 @@
         </is>
       </c>
       <c r="C435" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="D435" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="E435" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F435" t="n">
         <v>0.6</v>
-      </c>
-      <c r="F435" t="n">
-        <v>0.4</v>
       </c>
       <c r="G435" t="inlineStr">
         <is>
@@ -31843,16 +31843,16 @@
         </is>
       </c>
       <c r="C436" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="D436" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E436" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F436" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G436" t="inlineStr">
         <is>
@@ -31918,16 +31918,16 @@
         </is>
       </c>
       <c r="C437" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="D437" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="E437" t="n">
         <v>0.8</v>
       </c>
       <c r="F437" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="G437" t="inlineStr">
         <is>
@@ -31993,16 +31993,16 @@
         </is>
       </c>
       <c r="C438" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="D438" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E438" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F438" t="n">
         <v>0.7</v>
-      </c>
-      <c r="F438" t="n">
-        <v>0.6</v>
       </c>
       <c r="G438" t="inlineStr">
         <is>
@@ -32068,16 +32068,16 @@
         </is>
       </c>
       <c r="C439" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D439" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E439" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F439" t="n">
         <v>0.4</v>
-      </c>
-      <c r="D439" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E439" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F439" t="n">
-        <v>0.3</v>
       </c>
       <c r="G439" t="inlineStr">
         <is>
@@ -32143,13 +32143,13 @@
         </is>
       </c>
       <c r="C440" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D440" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E440" t="n">
         <v>0.9</v>
-      </c>
-      <c r="D440" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E440" t="n">
-        <v>0.8</v>
       </c>
       <c r="F440" t="n">
         <v>0.9</v>
@@ -32293,16 +32293,16 @@
         </is>
       </c>
       <c r="C442" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D442" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E442" t="n">
         <v>0.7</v>
       </c>
       <c r="F442" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G442" t="inlineStr">
         <is>
@@ -32443,16 +32443,16 @@
         </is>
       </c>
       <c r="C444" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D444" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E444" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="F444" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G444" t="inlineStr">
         <is>
@@ -32518,13 +32518,13 @@
         </is>
       </c>
       <c r="C445" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D445" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E445" t="n">
         <v>0.9</v>
-      </c>
-      <c r="D445" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E445" t="n">
-        <v>0.8</v>
       </c>
       <c r="F445" t="n">
         <v>0.9</v>
@@ -32599,10 +32599,10 @@
         <v>0.8</v>
       </c>
       <c r="E446" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="F446" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G446" t="inlineStr">
         <is>
@@ -32743,16 +32743,16 @@
         </is>
       </c>
       <c r="C448" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D448" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E448" t="n">
         <v>0.7</v>
       </c>
       <c r="F448" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G448" t="inlineStr">
         <is>
@@ -32818,16 +32818,16 @@
         </is>
       </c>
       <c r="C449" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="D449" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="E449" t="n">
         <v>0.7</v>
       </c>
       <c r="F449" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="G449" t="inlineStr">
         <is>
@@ -32893,16 +32893,16 @@
         </is>
       </c>
       <c r="C450" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D450" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E450" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F450" t="n">
         <v>0.6</v>
-      </c>
-      <c r="D450" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E450" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F450" t="n">
-        <v>0.5</v>
       </c>
       <c r="G450" t="inlineStr">
         <is>
@@ -33043,16 +33043,16 @@
         </is>
       </c>
       <c r="C452" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D452" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E452" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F452" t="n">
         <v>0.6</v>
-      </c>
-      <c r="D452" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E452" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F452" t="n">
-        <v>0.7</v>
       </c>
       <c r="G452" t="inlineStr">
         <is>
@@ -33124,10 +33124,10 @@
         <v>0.8</v>
       </c>
       <c r="E453" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="F453" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="G453" t="inlineStr">
         <is>
@@ -33193,16 +33193,16 @@
         </is>
       </c>
       <c r="C454" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="D454" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="E454" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="F454" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="G454" t="inlineStr">
         <is>
@@ -33268,16 +33268,16 @@
         </is>
       </c>
       <c r="C455" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="D455" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E455" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F455" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G455" t="inlineStr">
         <is>
@@ -33343,16 +33343,16 @@
         </is>
       </c>
       <c r="C456" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="D456" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E456" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="F456" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="G456" t="inlineStr">
         <is>
@@ -33493,16 +33493,16 @@
         </is>
       </c>
       <c r="C458" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="D458" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="E458" t="n">
         <v>0.8</v>
       </c>
       <c r="F458" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="G458" t="inlineStr">
         <is>
@@ -33577,7 +33577,7 @@
         <v>0.7</v>
       </c>
       <c r="F459" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="G459" t="inlineStr">
         <is>
@@ -33643,16 +33643,16 @@
         </is>
       </c>
       <c r="C460" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D460" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E460" t="n">
         <v>0.6</v>
       </c>
-      <c r="D460" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E460" t="n">
-        <v>0.3</v>
-      </c>
       <c r="F460" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G460" t="inlineStr">
         <is>
@@ -33724,10 +33724,10 @@
         <v>0.9</v>
       </c>
       <c r="E461" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="F461" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="G461" t="inlineStr">
         <is>
@@ -33868,13 +33868,13 @@
         </is>
       </c>
       <c r="C463" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="D463" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E463" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F463" t="n">
         <v>0.8</v>
@@ -33952,7 +33952,7 @@
         <v>0.3</v>
       </c>
       <c r="F464" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="G464" t="inlineStr">
         <is>
@@ -34024,7 +34024,7 @@
         <v>0.9</v>
       </c>
       <c r="E465" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="F465" t="n">
         <v>0.8</v>
@@ -34093,16 +34093,16 @@
         </is>
       </c>
       <c r="C466" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="D466" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="E466" t="n">
         <v>0.8</v>
       </c>
       <c r="F466" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G466" t="inlineStr">
         <is>
@@ -34177,7 +34177,7 @@
         <v>0.8</v>
       </c>
       <c r="F467" t="n">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="G467" t="inlineStr">
         <is>
@@ -34243,16 +34243,16 @@
         </is>
       </c>
       <c r="C468" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="D468" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E468" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F468" t="n">
         <v>0.6</v>
-      </c>
-      <c r="F468" t="n">
-        <v>0.7</v>
       </c>
       <c r="G468" t="inlineStr">
         <is>
@@ -34327,7 +34327,7 @@
         <v>0.7</v>
       </c>
       <c r="F469" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G469" t="inlineStr">
         <is>
@@ -34393,16 +34393,16 @@
         </is>
       </c>
       <c r="C470" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="D470" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="E470" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F470" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G470" t="inlineStr">
         <is>
@@ -34474,7 +34474,7 @@
         <v>0.8</v>
       </c>
       <c r="E471" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F471" t="n">
         <v>0.9</v>
@@ -34543,13 +34543,13 @@
         </is>
       </c>
       <c r="C472" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D472" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E472" t="n">
         <v>0.9</v>
-      </c>
-      <c r="D472" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E472" t="n">
-        <v>0.8</v>
       </c>
       <c r="F472" t="n">
         <v>0.9</v>
@@ -34618,16 +34618,16 @@
         </is>
       </c>
       <c r="C473" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="D473" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="E473" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F473" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="G473" t="inlineStr">
         <is>
@@ -34693,16 +34693,16 @@
         </is>
       </c>
       <c r="C474" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="D474" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E474" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F474" t="n">
         <v>0.5</v>
-      </c>
-      <c r="F474" t="n">
-        <v>0.8</v>
       </c>
       <c r="G474" t="inlineStr">
         <is>
@@ -34774,10 +34774,10 @@
         <v>0.8</v>
       </c>
       <c r="E475" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="F475" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G475" t="inlineStr">
         <is>
@@ -34927,7 +34927,7 @@
         <v>0.3</v>
       </c>
       <c r="F477" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G477" t="inlineStr">
         <is>
@@ -34993,16 +34993,16 @@
         </is>
       </c>
       <c r="C478" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="D478" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E478" t="n">
         <v>0.7</v>
       </c>
       <c r="F478" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G478" t="inlineStr">
         <is>
@@ -35149,7 +35149,7 @@
         <v>0.9</v>
       </c>
       <c r="E480" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F480" t="n">
         <v>0.8</v>
@@ -35218,16 +35218,16 @@
         </is>
       </c>
       <c r="C481" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="D481" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="E481" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="F481" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G481" t="inlineStr">
         <is>
@@ -35293,10 +35293,10 @@
         </is>
       </c>
       <c r="C482" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="D482" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="E482" t="n">
         <v>0.7</v>
@@ -35377,7 +35377,7 @@
         <v>0.3</v>
       </c>
       <c r="F483" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="G483" t="inlineStr">
         <is>
@@ -35449,10 +35449,10 @@
         <v>0.8</v>
       </c>
       <c r="E484" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F484" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G484" t="inlineStr">
         <is>
@@ -35518,13 +35518,13 @@
         </is>
       </c>
       <c r="C485" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D485" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E485" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F485" t="n">
         <v>0.9</v>
@@ -35593,16 +35593,16 @@
         </is>
       </c>
       <c r="C486" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="D486" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E486" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="F486" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="G486" t="inlineStr">
         <is>
@@ -35677,7 +35677,7 @@
         <v>0.3</v>
       </c>
       <c r="F487" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G487" t="inlineStr">
         <is>
@@ -35743,16 +35743,16 @@
         </is>
       </c>
       <c r="C488" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="D488" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="E488" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F488" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G488" t="inlineStr">
         <is>
@@ -35818,16 +35818,16 @@
         </is>
       </c>
       <c r="C489" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="D489" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E489" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F489" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G489" t="inlineStr">
         <is>
@@ -35893,16 +35893,16 @@
         </is>
       </c>
       <c r="C490" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="D490" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E490" t="n">
         <v>0.4</v>
       </c>
       <c r="F490" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="G490" t="inlineStr">
         <is>
@@ -36043,16 +36043,16 @@
         </is>
       </c>
       <c r="C492" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="D492" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E492" t="n">
         <v>0.3</v>
       </c>
       <c r="F492" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G492" t="inlineStr">
         <is>
@@ -36118,16 +36118,16 @@
         </is>
       </c>
       <c r="C493" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D493" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E493" t="n">
         <v>0.7</v>
       </c>
       <c r="F493" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G493" t="inlineStr">
         <is>
@@ -36343,10 +36343,10 @@
         </is>
       </c>
       <c r="C496" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D496" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E496" t="n">
         <v>0.7</v>
@@ -36418,16 +36418,16 @@
         </is>
       </c>
       <c r="C497" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="D497" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="E497" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="F497" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G497" t="inlineStr">
         <is>
@@ -36493,16 +36493,16 @@
         </is>
       </c>
       <c r="C498" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="D498" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E498" t="n">
         <v>0.5</v>
       </c>
       <c r="F498" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G498" t="inlineStr">
         <is>
@@ -36568,16 +36568,16 @@
         </is>
       </c>
       <c r="C499" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="D499" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="E499" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F499" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G499" t="inlineStr">
         <is>
@@ -36643,16 +36643,16 @@
         </is>
       </c>
       <c r="C500" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D500" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E500" t="n">
         <v>0.7</v>
       </c>
-      <c r="D500" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E500" t="n">
-        <v>0.8</v>
-      </c>
       <c r="F500" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="G500" t="inlineStr">
         <is>
@@ -36718,16 +36718,16 @@
         </is>
       </c>
       <c r="C501" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D501" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E501" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F501" t="n">
         <v>0.9</v>
-      </c>
-      <c r="D501" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E501" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F501" t="n">
-        <v>0.8</v>
       </c>
       <c r="G501" t="inlineStr">
         <is>
@@ -36799,10 +36799,10 @@
         <v>0.8</v>
       </c>
       <c r="E502" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F502" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G502" t="inlineStr">
         <is>
@@ -36868,16 +36868,16 @@
         </is>
       </c>
       <c r="C503" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="D503" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E503" t="n">
         <v>0.7</v>
       </c>
       <c r="F503" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G503" t="inlineStr">
         <is>
@@ -36943,16 +36943,16 @@
         </is>
       </c>
       <c r="C504" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D504" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E504" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F504" t="n">
         <v>0.9</v>
-      </c>
-      <c r="D504" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E504" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F504" t="n">
-        <v>0.8</v>
       </c>
       <c r="G504" t="inlineStr">
         <is>
@@ -37099,10 +37099,10 @@
         <v>0.6</v>
       </c>
       <c r="E506" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F506" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G506" t="inlineStr">
         <is>
@@ -37168,16 +37168,16 @@
         </is>
       </c>
       <c r="C507" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D507" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E507" t="n">
         <v>0.5</v>
       </c>
       <c r="F507" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G507" t="inlineStr">
         <is>
@@ -37249,7 +37249,7 @@
         <v>0.8</v>
       </c>
       <c r="E508" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="F508" t="n">
         <v>0.9</v>
@@ -37393,16 +37393,16 @@
         </is>
       </c>
       <c r="C510" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D510" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E510" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F510" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G510" t="inlineStr">
         <is>
@@ -37618,10 +37618,10 @@
         </is>
       </c>
       <c r="C513" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="D513" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E513" t="n">
         <v>0.7</v>
@@ -37693,16 +37693,16 @@
         </is>
       </c>
       <c r="C514" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="D514" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E514" t="n">
         <v>0.8</v>
       </c>
       <c r="F514" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G514" t="inlineStr">
         <is>
@@ -37774,10 +37774,10 @@
         <v>0.8</v>
       </c>
       <c r="E515" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F515" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G515" t="inlineStr">
         <is>
@@ -37843,16 +37843,16 @@
         </is>
       </c>
       <c r="C516" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="D516" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E516" t="n">
         <v>0.7</v>
       </c>
       <c r="F516" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G516" t="inlineStr">
         <is>
@@ -37924,7 +37924,7 @@
         <v>0.8</v>
       </c>
       <c r="E517" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="F517" t="n">
         <v>0.9</v>
@@ -37999,10 +37999,10 @@
         <v>0.8</v>
       </c>
       <c r="E518" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="F518" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="G518" t="inlineStr">
         <is>
@@ -38077,7 +38077,7 @@
         <v>0.7</v>
       </c>
       <c r="F519" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G519" t="inlineStr">
         <is>
@@ -38149,7 +38149,7 @@
         <v>0.8</v>
       </c>
       <c r="E520" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="F520" t="n">
         <v>0.9</v>
@@ -38218,13 +38218,13 @@
         </is>
       </c>
       <c r="C521" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D521" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E521" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F521" t="n">
         <v>0.9</v>
@@ -38293,10 +38293,10 @@
         </is>
       </c>
       <c r="C522" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="D522" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E522" t="n">
         <v>0.7</v>
@@ -38443,16 +38443,16 @@
         </is>
       </c>
       <c r="C524" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D524" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E524" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F524" t="n">
         <v>0.9</v>
-      </c>
-      <c r="D524" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E524" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F524" t="n">
-        <v>0.8</v>
       </c>
       <c r="G524" t="inlineStr">
         <is>
@@ -38599,7 +38599,7 @@
         <v>0.8</v>
       </c>
       <c r="E526" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="F526" t="n">
         <v>0.9</v>
@@ -38677,7 +38677,7 @@
         <v>0.7</v>
       </c>
       <c r="F527" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="G527" t="inlineStr">
         <is>
@@ -38743,16 +38743,16 @@
         </is>
       </c>
       <c r="C528" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D528" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E528" t="n">
         <v>0.5</v>
       </c>
       <c r="F528" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="G528" t="inlineStr">
         <is>
@@ -38818,16 +38818,16 @@
         </is>
       </c>
       <c r="C529" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D529" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E529" t="n">
         <v>0.8</v>
       </c>
       <c r="F529" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G529" t="inlineStr">
         <is>
@@ -38896,13 +38896,13 @@
         <v>0.8</v>
       </c>
       <c r="D530" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="E530" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="F530" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G530" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>0.9</v>
       </c>
       <c r="E531" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="F531" t="n">
         <v>0.8</v>
@@ -39046,13 +39046,13 @@
         <v>0.8</v>
       </c>
       <c r="D532" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="E532" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="F532" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G532" t="inlineStr">
         <is>
@@ -39124,10 +39124,10 @@
         <v>0.9</v>
       </c>
       <c r="E533" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="F533" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="G533" t="inlineStr">
         <is>
@@ -39199,7 +39199,7 @@
         <v>0.9</v>
       </c>
       <c r="E534" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="F534" t="n">
         <v>0.8</v>
@@ -39274,7 +39274,7 @@
         <v>0.8</v>
       </c>
       <c r="E535" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="F535" t="n">
         <v>0.9</v>
@@ -39352,7 +39352,7 @@
         <v>0.7</v>
       </c>
       <c r="F536" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G536" t="inlineStr">
         <is>
@@ -39418,16 +39418,16 @@
         </is>
       </c>
       <c r="C537" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="D537" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E537" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="F537" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="G537" t="inlineStr">
         <is>
@@ -39493,13 +39493,13 @@
         </is>
       </c>
       <c r="C538" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D538" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E538" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F538" t="n">
         <v>0.9</v>
@@ -39568,13 +39568,13 @@
         </is>
       </c>
       <c r="C539" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D539" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E539" t="n">
         <v>0.9</v>
-      </c>
-      <c r="D539" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E539" t="n">
-        <v>0.8</v>
       </c>
       <c r="F539" t="n">
         <v>0.9</v>
@@ -39643,16 +39643,16 @@
         </is>
       </c>
       <c r="C540" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="D540" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E540" t="n">
         <v>0.3</v>
       </c>
       <c r="F540" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="G540" t="inlineStr">
         <is>
@@ -39793,16 +39793,16 @@
         </is>
       </c>
       <c r="C542" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="D542" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E542" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F542" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G542" t="inlineStr">
         <is>
@@ -39868,16 +39868,16 @@
         </is>
       </c>
       <c r="C543" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="D543" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E543" t="n">
         <v>0.3</v>
       </c>
       <c r="F543" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="G543" t="inlineStr">
         <is>
@@ -39952,7 +39952,7 @@
         <v>0.7</v>
       </c>
       <c r="F544" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="G544" t="inlineStr">
         <is>
@@ -40027,7 +40027,7 @@
         <v>0.2</v>
       </c>
       <c r="F545" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="G545" t="inlineStr">
         <is>
@@ -40093,16 +40093,16 @@
         </is>
       </c>
       <c r="C546" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="D546" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E546" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F546" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="G546" t="inlineStr">
         <is>
@@ -40174,7 +40174,7 @@
         <v>0.8</v>
       </c>
       <c r="E547" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="F547" t="n">
         <v>0.9</v>
@@ -40327,7 +40327,7 @@
         <v>0.3</v>
       </c>
       <c r="F549" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="G549" t="inlineStr">
         <is>
@@ -40393,13 +40393,13 @@
         </is>
       </c>
       <c r="C550" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="D550" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E550" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F550" t="n">
         <v>0.9</v>
@@ -40474,7 +40474,7 @@
         <v>0.8</v>
       </c>
       <c r="E551" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="F551" t="n">
         <v>0.9</v>
@@ -40549,10 +40549,10 @@
         <v>0.9</v>
       </c>
       <c r="E552" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="F552" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G552" t="inlineStr">
         <is>
@@ -40693,16 +40693,16 @@
         </is>
       </c>
       <c r="C554" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="D554" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E554" t="n">
         <v>0.9</v>
       </c>
-      <c r="D554" t="n">
+      <c r="F554" t="n">
         <v>0.9</v>
-      </c>
-      <c r="E554" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F554" t="n">
-        <v>0.85</v>
       </c>
       <c r="G554" t="inlineStr">
         <is>
@@ -40774,10 +40774,10 @@
         <v>0.9</v>
       </c>
       <c r="E555" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="F555" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G555" t="inlineStr">
         <is>
@@ -40849,7 +40849,7 @@
         <v>0.8</v>
       </c>
       <c r="E556" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="F556" t="n">
         <v>0.9</v>
@@ -40918,13 +40918,13 @@
         </is>
       </c>
       <c r="C557" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="D557" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E557" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F557" t="n">
         <v>0.9</v>
@@ -40999,7 +40999,7 @@
         <v>0.8</v>
       </c>
       <c r="E558" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="F558" t="n">
         <v>0.9</v>
@@ -41068,13 +41068,13 @@
         </is>
       </c>
       <c r="C559" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="D559" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E559" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F559" t="n">
         <v>0.9</v>
@@ -41143,16 +41143,16 @@
         </is>
       </c>
       <c r="C560" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="D560" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E560" t="n">
         <v>0.8</v>
       </c>
       <c r="F560" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="G560" t="inlineStr">
         <is>
@@ -41224,10 +41224,10 @@
         <v>0.8</v>
       </c>
       <c r="E561" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="F561" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="G561" t="inlineStr">
         <is>
@@ -41293,16 +41293,16 @@
         </is>
       </c>
       <c r="C562" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="D562" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E562" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F562" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G562" t="inlineStr">
         <is>
@@ -41449,7 +41449,7 @@
         <v>0.9</v>
       </c>
       <c r="E564" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F564" t="n">
         <v>0.8</v>
@@ -41524,7 +41524,7 @@
         <v>0.8</v>
       </c>
       <c r="E565" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F565" t="n">
         <v>0.9</v>
@@ -41593,16 +41593,16 @@
         </is>
       </c>
       <c r="C566" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D566" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E566" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="F566" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="G566" t="inlineStr">
         <is>
@@ -41668,16 +41668,16 @@
         </is>
       </c>
       <c r="C567" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D567" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E567" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F567" t="n">
         <v>0.9</v>
-      </c>
-      <c r="D567" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E567" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F567" t="n">
-        <v>0.6</v>
       </c>
       <c r="G567" t="inlineStr">
         <is>
@@ -41743,13 +41743,13 @@
         </is>
       </c>
       <c r="C568" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D568" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E568" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F568" t="n">
         <v>0.9</v>
@@ -41818,16 +41818,16 @@
         </is>
       </c>
       <c r="C569" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D569" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E569" t="n">
         <v>0.3</v>
       </c>
       <c r="F569" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G569" t="inlineStr">
         <is>
@@ -41899,10 +41899,10 @@
         <v>0.9</v>
       </c>
       <c r="E570" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="F570" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G570" t="inlineStr">
         <is>
@@ -42052,7 +42052,7 @@
         <v>0.3</v>
       </c>
       <c r="F572" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="G572" t="inlineStr">
         <is>
@@ -42277,7 +42277,7 @@
         <v>0.3</v>
       </c>
       <c r="F575" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="G575" t="inlineStr">
         <is>
@@ -42349,10 +42349,10 @@
         <v>0.8</v>
       </c>
       <c r="E576" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F576" t="n">
         <v>0.7</v>
-      </c>
-      <c r="F576" t="n">
-        <v>0.9</v>
       </c>
       <c r="G576" t="inlineStr">
         <is>
@@ -42418,13 +42418,13 @@
         </is>
       </c>
       <c r="C577" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="D577" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="E577" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F577" t="n">
         <v>0.9</v>
@@ -42568,16 +42568,16 @@
         </is>
       </c>
       <c r="C579" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="D579" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E579" t="n">
         <v>0.3</v>
       </c>
       <c r="F579" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G579" t="inlineStr">
         <is>
@@ -42643,13 +42643,13 @@
         </is>
       </c>
       <c r="C580" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D580" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E580" t="n">
         <v>0.9</v>
-      </c>
-      <c r="D580" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E580" t="n">
-        <v>0.7</v>
       </c>
       <c r="F580" t="n">
         <v>0.9</v>
@@ -42718,13 +42718,13 @@
         </is>
       </c>
       <c r="C581" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D581" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E581" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F581" t="n">
         <v>0.9</v>
@@ -42793,16 +42793,16 @@
         </is>
       </c>
       <c r="C582" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D582" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E582" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F582" t="n">
         <v>0.9</v>
-      </c>
-      <c r="D582" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E582" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F582" t="n">
-        <v>0.8</v>
       </c>
       <c r="G582" t="inlineStr">
         <is>
@@ -42874,7 +42874,7 @@
         <v>0.8</v>
       </c>
       <c r="E583" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="F583" t="n">
         <v>0.9</v>
@@ -43024,10 +43024,10 @@
         <v>0.9</v>
       </c>
       <c r="E585" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="F585" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G585" t="inlineStr">
         <is>
@@ -43093,16 +43093,16 @@
         </is>
       </c>
       <c r="C586" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="D586" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="E586" t="n">
         <v>0.8</v>
       </c>
       <c r="F586" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G586" t="inlineStr">
         <is>
